--- a/Relatorio_Perdas.xlsx
+++ b/Relatorio_Perdas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1509,6 +1509,336 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alface</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>171</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tomate cereja</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>215</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Estragou</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>346</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Estragou</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rúcula</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mini-Banoffe</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Venceu na vitrine</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Torta Cheescake</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jaqueline</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ressecadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pão de queijo 15g</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>38</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Muito tempo na geladeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pão de queijo 75g</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Muito tempo na geladeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Copo shot</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Alexandro</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Quebrou durante lavagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Copo shot</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Alexandro</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Encontrado quebrado na mesa ao recolher louça do cliente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Relatorio_Perdas.xlsx
+++ b/Relatorio_Perdas.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +466,138 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>obs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Empada frango</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Quebrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pires grande</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lascado na borda</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manjericão</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rúcula</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
     </row>

--- a/Relatorio_Perdas.xlsx
+++ b/Relatorio_Perdas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,105 @@
       <c r="G5" t="inlineStr">
         <is>
           <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Display de mesa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Quebrado na mesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Estragado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Coca normal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Latas estufadas</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Perdas.xlsx
+++ b/Relatorio_Perdas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,996 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bolo de fubá</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Deixou cair</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Leite integral</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Estragado (Talhado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Xícara pequena</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Quebrou durante manuseio</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Leite integral</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Estava talhado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Suco abacaxi com hortelã</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cliente alegou que estava ruim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Manjericão</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Folhas amareladas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bolo de chocolate com cenoura</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jaqueline</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mofado (Problema de qualidade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Xícara grande</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Deixou cair</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pires grande</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Deixou cair</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cappuccino Scada</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Deixou cair</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Copo shot</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Quebrado na bandeja de copos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Presunto</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Leite integral</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Talhado (Problema de qualidade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Folhado Napoli</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Queimou</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Casadinho</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Deixou cair</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Manjericão</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hortifruti</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Folhas murchas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Empada de frango</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tempo de vitrine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Torta de Limão</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cliente reclamou do sabor e textura da torta, alegando que estava velha. Tiramos outra para prova e nada de anormal foi identificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Boleira</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Quebrou a tampa durante a lavagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Molho pesto</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Vencido (estragado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cappuccino Diet</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Caiu no chão</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pires grande</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Borda lascada</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Molho pesto</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Venceu</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Peito de peru</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Venceu (validade)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Estragou</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Goma tapioca</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Insumo</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jeisiana</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fez errado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Prato refeição (funghi)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Utensilio</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Quebra</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jaqueline</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Deixou cair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brownie</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Naiane</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Deixou cair</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Latte simples</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Produto final</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Erro de processo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Derramou</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
